--- a/PP_a_Vox_resultados_por_circunscripcion.xlsx
+++ b/PP_a_Vox_resultados_por_circunscripcion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vivab\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC05986D-50A8-42C5-945F-D91EB729DFBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11A6A8AD-18CF-4884-B672-8B4D15FED04D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -624,6 +624,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:J53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2149,6 +2152,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" scale="46" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
